--- a/光伏配储项目/电价数据/2026/东湖站.xlsx
+++ b/光伏配储项目/电价数据/2026/东湖站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.94545</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.24008</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.05438</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.88854</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.53266</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45906</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42598</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42451</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40444</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42754</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38754</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42401</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31175</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.12255</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.13474</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14085</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.07365000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.11352</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.54265</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.21238</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28695</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05087</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7643300000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.19105</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14779</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22942</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23466</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21863</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.67886</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.42048</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14874</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29071</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.5316000000000001</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6835</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7745700000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.95561</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.65975</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43647</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65823</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.1836</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.7914800000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.37101</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.60052</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.7594299999999999</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.00287</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.06077</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.79057</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.32866</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8712000000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79648</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75705</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51754</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47953</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46887</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42537</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70821</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76911</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.87124</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91596</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5147</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50257</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48508</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40812</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.87666</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7199500000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8154199999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45621</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50869</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5056700000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.77681</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.99087</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.88822</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8445499999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49612</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7231599999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.30906</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.02449</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.46957</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54498</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5220900000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.92223</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62222</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.33294</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.55295</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.1767</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.12531</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.59903</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.50121</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.65659</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.43488</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.48611</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.04288</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.37859</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90212</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.46252</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.55582</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.36804</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.15162</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45018</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78695</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.80776</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44361</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3346</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50769</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48673</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48716</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41409</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42763</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44306</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38345</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47207</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34729</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39425</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35273</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.50466</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.68916</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.9064099999999999</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.82176</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7600800000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.25049</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.55367</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.49519</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.81774</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.59078</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8115399999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5278099999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54772</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79903</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.23433</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6819299999999999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5976900000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49345</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.78765</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52098</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50412</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57008</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.5952999999999999</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54257</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5624</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26489</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.18191</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.5043</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57602</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9784700000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.04126</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.40741</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.86482</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.8391799999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.67691</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.93179</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6102300000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.9085299999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56259</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.31553</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8734400000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55938</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48189</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.5150399999999999</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39739</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34195</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52162</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49373</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38928</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38752</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36305</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3933</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.52639</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.76381</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.64328</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.88347</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.22029</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.81057</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.94284</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.42632</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.7063700000000001</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.43929</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.27887</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.1898</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.03268</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.52572</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.97881</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.45675</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60436</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.42345</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.47978</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40463</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.9584400000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.9619800000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.84357</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.40472</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.47913</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42799</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49517</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45025</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46173</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47411</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5197200000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.04044</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.93996</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.47163</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.00664</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.89462</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50074</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.81687</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.7663099999999999</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.6542899999999999</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41595</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.55148</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31754</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.72436</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.84866</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.44413</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.19823</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.45291</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.42249</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.21985</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15556</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.40167</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.2705</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.18917</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.51315</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.48622</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.05035</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22406</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.44627</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2101</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06343</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.10188</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.00107</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.04105</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26973</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37784</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39266</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46143</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39245</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48663</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34443</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.59128</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30536</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10274</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04356</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01523</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21614</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05421</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.06587</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07029000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06853000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33162</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3131</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38678</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42758</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78523</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87754</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.15774</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.84735</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44963</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41967</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36289</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40943</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44936</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.56012</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58499</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70929</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8766900000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5535099999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8198300000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5728799999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85329</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.63195</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30301</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6344500000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59241</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.30177</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.28887</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42469</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39336</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34726</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91407</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44506</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39445</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39107</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35577</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34898</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.46385</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33021</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31043</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18833</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35771</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2731</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28155</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30897</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2538</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32116</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.11027</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44064</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.53691</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.86761</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.44381</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14005</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6871799999999999</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.77751</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.63886</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44067</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49064</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43091</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40574</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.46476</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42582</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42641</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41655</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.40685</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4075</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.39568</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48706</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5256799999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.23181</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15513</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27443</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01053</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25996</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25307</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38844</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5441</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43457</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.7897799999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.43588</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41639</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30832</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.29711</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.28883</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29273</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30914</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.28424</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30101</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.24794</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24247</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26489</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.23605</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.23156</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.23832</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.28562</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.2456</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.44824</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42457</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36683</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41911</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.41116</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.41559</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4382200000000001</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38321</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39084</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38473</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.33548</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.49428</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36643</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.42118</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36496</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33279</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.86256</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23953</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30365</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.52674</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.54735</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.59862</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.54715</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3346</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.8570800000000001</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.9295399999999999</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.8845</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.12225</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.77606</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.15791</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.46331</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.43407</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.43316</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.73003</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.48303</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42412</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34945</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.46369</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.47624</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33862</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33697</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36258</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3741</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.40604</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.69799</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.8091699999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.7972400000000001</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.51874</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7310599999999999</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.46485</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.14159</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.81301</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.79688</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.10749</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.7675599999999999</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.3031</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.17379</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.20893</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.7185900000000001</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.12951</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.39457</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.30915</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.61948</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.49145</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.29119</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.53181</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.69051</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.55356</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.70711</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.30147</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.60715</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.04494</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.77973</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.37639</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.78754</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.75421</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.8429099999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.7698400000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.7650800000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.3336</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.8915700000000001</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.7446</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.87154</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.85346</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.12824</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.80062</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.6636</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.61463</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.52236</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36857</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50383</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24115</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>1.6083</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31265</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.9389299999999999</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.38439</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.29893</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>1.08952</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.49833</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.87952</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.23722</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47743</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.14918</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.5340900000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.90516</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.90218</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34351</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34473</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.28309</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33729</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32603</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31587</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31926</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75326</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.32681</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.42184</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5506799999999999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42645</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.49892</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.59277</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.42274</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.45135</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.40984</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34261</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.50893</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37236</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.63449</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65104</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.70108</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.6270800000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.72289</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35314</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36101</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35301</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35268</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34336</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.48131</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.48341</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.88634</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.58663</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.9518300000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.4788</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.69143</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>1.01709</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.29364</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.71478</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.76642</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.58057</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.93099</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.79528</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.37452</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.7190700000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.99398</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.74883</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.98651</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.44649</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.42008</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.45088</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.05069</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.00851</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.43888</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.92028</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.11049</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.93269</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.8952599999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.80657</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.49485</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.41562</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.7736000000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40833</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36715</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35113</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.45674</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.53027</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.47661</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6206499999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39018</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.38847</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39506</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.41609</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.50641</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46151</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42229</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.60005</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.32183</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.97781</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.36906</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.40569</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.48538</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34886</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.91472</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.9159700000000001</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.93743</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.60915</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.82736</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.85864</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.8497400000000001</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.9290900000000001</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.17822</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.21234</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.54331</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.90263</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.90399</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.89436</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.8936000000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.36569</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.45975</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47386</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.4741</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.50737</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.62593</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73495</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.82436</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.59192</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.71635</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.11225</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.44607</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.73707</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76532</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61811</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6664600000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.65003</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.03317</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.44598</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.43913</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.50771</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42838</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4197</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41005</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37574</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.43757</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36417</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3514</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.90973</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.87925</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.87588</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.89601</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.8851</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.39856</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.89706</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.97634</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.93367</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.98641</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21729</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.90615</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.5492999999999999</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42515</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41138</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.4259</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39431</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37423</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.32766</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.37692</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.35382</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3337</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46166</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37618</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="G135" t="n">
+        <v>1.58463</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.31357</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.28564</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.27054</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.29987</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.30441</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.26187</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.25219</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.18985</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2449</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26162</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.2579</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.09937</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25704</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03474</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.19385</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24874</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25852</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24019</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28494</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27592</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31788</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.41276</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.45096</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.67359</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.67652</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43198</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.50785</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31069</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.32499</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="C136" t="n">
+        <v>1.16587</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32874</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.29548</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.24429</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.25361</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.24378</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.24643</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.24313</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.24313</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.2451</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.23987</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.24313</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.24345</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28346</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.24393</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.24372</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.25068</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.16708</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.21424</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01296</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00022</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14591</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02127</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04075</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02924</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03822</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01885</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03614</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20153</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26488</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2884</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2792</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24776</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3113</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36599</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.42134</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.33216</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7384500000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.63522</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38742</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.4315</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39482</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41583</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42516</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.26549</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.24524</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.26969</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26624</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43693</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.27007</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36934</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.68436</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.84185</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8772000000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85097</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.11416</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21736</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29938</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04908</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.27105</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00126</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-3e-05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31395</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.50143</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79218</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.74673</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.7708700000000001</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.34256</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.98033</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.76279</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.83523</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.79455</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84039</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8385900000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84289</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94009</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.75485</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.7905</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7578400000000001</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39347</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36408</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.46735</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.61198</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.66122</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.57368</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49378</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.46274</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39322</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37382</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.28598</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.46306</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.47485</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.36812</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42584</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.45204</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.41411</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39462</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35729</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26628</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37435</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37129</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.42849</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.45388</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7163200000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.5910700000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.4589</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41058</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33825</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42067</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33676</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.55416</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7646499999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.5396799999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50075</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.47709</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.61175</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.5777</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.60192</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.65143</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.48489</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.56532</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.58641</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.91575</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.32824</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.39185</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.05551</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.49082</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.72335</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.71186</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.55862</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.45595</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.9345800000000001</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>1.25804</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>1.54171</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.65142</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.52603</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42128</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38096</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23527</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3527</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.45437</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34035</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36248</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.45796</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.86578</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.50229</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.9731300000000001</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.60533</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.46118</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.7496</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.5774</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41836</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5121</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.18175</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70778</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.00311</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47569</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.26382</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.47436</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.36867</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.29276</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.83285</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>1.08817</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.9973200000000001</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.49106</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35709</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33914</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33261</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.23356</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.56978</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.8124</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>1.65046</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.84829</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.6799500000000001</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.81674</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.90783</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.81272</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.83333</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.5922799999999999</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.49388</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.5890599999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.51998</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.52838</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37157</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.8800399999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.74022</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.8985299999999999</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.92488</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.78657</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.48573</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.9576</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.9060900000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.94435</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.90892</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.64547</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39949</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.52301</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.68589</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36388</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.42352</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.27688</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5592699999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.7847799999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.61997</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37314</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36491</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36234</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37584</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.4067</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.52573</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.06506</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.7355</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.0194</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32336</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.5662999999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42686</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36373</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.54279</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.63102</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.92077</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.7793600000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.7289600000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.54888</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.53959</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.71983</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.7447699999999999</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.9741000000000001</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.30509</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.14389</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35897</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.37149</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36778</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36832</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36274</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>1.36556</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3576</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.35543</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>1.34952</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14526</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19792</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29105</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04456</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12129</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22579</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.15086</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.19573</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>1.30407</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22606</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.26199</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15292</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30763</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.1527</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.31247</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19665</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14261</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27957</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.63962</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.5786699999999999</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.52081</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.53837</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>1.68613</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>1.08277</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.7038300000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.5144299999999999</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.77228</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.5646599999999999</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41733</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.5720499999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.54906</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40138</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.67638</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5577799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5515599999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.61491</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38356</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38453</v>
       </c>
     </row>
   </sheetData>
